--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260307_201350.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260307_201350.xlsx
@@ -5548,7 +5548,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260307_201350.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260307_201350.xlsx
@@ -5548,7 +5548,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
